--- a/results/consolidated/Consolidated_NF_GARCH_Results.xlsx
+++ b/results/consolidated/Consolidated_NF_GARCH_Results.xlsx
@@ -440,13 +440,13 @@
         <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>-8536.82881066782</v>
+        <v>-6287.35443106992</v>
       </c>
       <c r="G2" t="n">
-        <v>-8508.24033352615</v>
+        <v>-6259.41251168897</v>
       </c>
       <c r="H2" t="n">
-        <v>4274.41440533391</v>
+        <v>3149.67721553496</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -504,13 +504,13 @@
         <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>-9208.22580628112</v>
+        <v>-6799.03556910042</v>
       </c>
       <c r="G4" t="n">
-        <v>-9179.63732913944</v>
+        <v>-6771.09364971946</v>
       </c>
       <c r="H4" t="n">
-        <v>4610.11290314056</v>
+        <v>3405.51778455021</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -536,13 +536,13 @@
         <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>-8408.52927162422</v>
+        <v>-6175.98575109436</v>
       </c>
       <c r="G5" t="n">
-        <v>-8387.08791376796</v>
+        <v>-6155.02931155864</v>
       </c>
       <c r="H5" t="n">
-        <v>4208.76463581211</v>
+        <v>3092.49287554718</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>

--- a/results/consolidated/Consolidated_NF_GARCH_Results.xlsx
+++ b/results/consolidated/Consolidated_NF_GARCH_Results.xlsx
@@ -440,13 +440,13 @@
         <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>-6287.35443106992</v>
+        <v>-16492.244919545</v>
       </c>
       <c r="G2" t="n">
-        <v>-6259.41251168897</v>
+        <v>-16456.3401877928</v>
       </c>
       <c r="H2" t="n">
-        <v>3149.67721553496</v>
+        <v>8252.12245977249</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -472,13 +472,13 @@
         <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>1184.14011817545</v>
+        <v>635.787255489474</v>
       </c>
       <c r="G3" t="n">
-        <v>1209.42776676599</v>
+        <v>671.691987241692</v>
       </c>
       <c r="H3" t="n">
-        <v>-586.070059087727</v>
+        <v>-311.893627744737</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -504,13 +504,13 @@
         <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>-6799.03556910042</v>
+        <v>-17512.3222721118</v>
       </c>
       <c r="G4" t="n">
-        <v>-6771.09364971946</v>
+        <v>-17476.4175403596</v>
       </c>
       <c r="H4" t="n">
-        <v>3405.51778455021</v>
+        <v>8762.1611360559</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -536,13 +536,13 @@
         <v>11</v>
       </c>
       <c r="F5" t="n">
-        <v>-6175.98575109436</v>
+        <v>-16259.1952479916</v>
       </c>
       <c r="G5" t="n">
-        <v>-6155.02931155864</v>
+        <v>-16232.2666991774</v>
       </c>
       <c r="H5" t="n">
-        <v>3092.49287554718</v>
+        <v>8134.0976239958</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
